--- a/admin/src/zoom/respCode/response_code.xlsx
+++ b/admin/src/zoom/respCode/response_code.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mebugs\siteol\smart\src\zoom\respCode\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mebugs\mebugs\admin\src\zoom\respCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="response_code" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="456">
   <si>
     <t>ID</t>
   </si>
@@ -1043,13 +1044,370 @@
   </si>
   <si>
     <t>Password reset failed, please contact the administrator</t>
+  </si>
+  <si>
+    <t>CategoryAddSS</t>
+  </si>
+  <si>
+    <t>CategoryEditSS</t>
+  </si>
+  <si>
+    <t>CategoryDelSS</t>
+  </si>
+  <si>
+    <t>CategoryMergeSS</t>
+  </si>
+  <si>
+    <t>CategoryGetNG</t>
+  </si>
+  <si>
+    <t>CategoryMergeNG</t>
+  </si>
+  <si>
+    <t>CategoryAddNoScNG</t>
+  </si>
+  <si>
+    <t>CategoryUniXxxNG</t>
+  </si>
+  <si>
+    <t>CategoryDelNoNG</t>
+  </si>
+  <si>
+    <t>CategoryDelNG</t>
+  </si>
+  <si>
+    <t>文章分类创建成功</t>
+  </si>
+  <si>
+    <t>文章分类编辑成功</t>
+  </si>
+  <si>
+    <t>文章分类删除成功</t>
+  </si>
+  <si>
+    <t>文章分类迁移成功</t>
+  </si>
+  <si>
+    <t>文章分类查询失败</t>
+  </si>
+  <si>
+    <t>文章分类迁移失败</t>
+  </si>
+  <si>
+    <t>文章分类未提交图片</t>
+  </si>
+  <si>
+    <t>文章分类地址全局唯一</t>
+  </si>
+  <si>
+    <t>文章分类删除失败</t>
+  </si>
+  <si>
+    <t>文章分类下存在数据禁止删除</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>SourceAddSS</t>
+  </si>
+  <si>
+    <t>//</t>
+  </si>
+  <si>
+    <t>资源配置表创建成功</t>
+  </si>
+  <si>
+    <t>SourceEditSS</t>
+  </si>
+  <si>
+    <t>资源配置表编辑成功</t>
+  </si>
+  <si>
+    <t>SourceDelSS</t>
+  </si>
+  <si>
+    <t>资源清理暂不开放</t>
+  </si>
+  <si>
+    <t>SourceGetNG</t>
+  </si>
+  <si>
+    <t>资源配置表查询失败</t>
+  </si>
+  <si>
+    <t>SourceFileUpNg</t>
+  </si>
+  <si>
+    <t>资源文件上传失败</t>
+  </si>
+  <si>
+    <t>资源添加成功</t>
+  </si>
+  <si>
+    <t>资源编辑成功</t>
+  </si>
+  <si>
+    <t>资源查询失败</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>TagAddSS</t>
+  </si>
+  <si>
+    <t>标签创建成功</t>
+  </si>
+  <si>
+    <t>TagEditSS</t>
+  </si>
+  <si>
+    <t>标签编辑成功</t>
+  </si>
+  <si>
+    <t>TagDelSS</t>
+  </si>
+  <si>
+    <t>标签删除成功</t>
+  </si>
+  <si>
+    <t>TagGetNG</t>
+  </si>
+  <si>
+    <t>标签查询失败</t>
+  </si>
+  <si>
+    <t>TagAddNoScNG</t>
+  </si>
+  <si>
+    <t>文章标签未提交图片</t>
+  </si>
+  <si>
+    <t>TagUniUrlNG</t>
+  </si>
+  <si>
+    <t>标签地址全局唯一</t>
+  </si>
+  <si>
+    <t>文章标签下存在数据禁止删除</t>
+  </si>
+  <si>
+    <t>TagDelNG</t>
+  </si>
+  <si>
+    <t>文章标签创建成功</t>
+  </si>
+  <si>
+    <t>文章标签编辑成功</t>
+  </si>
+  <si>
+    <t>文章标签删除成功</t>
+  </si>
+  <si>
+    <t>文章标签查询失败</t>
+  </si>
+  <si>
+    <t>文章标签地址全局唯一</t>
+  </si>
+  <si>
+    <t>文章标签删除失败</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>文章标签下数据删除失败</t>
+  </si>
+  <si>
+    <t>TagDelPostNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TopicAddSS     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TopicEditSS    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TopicDelSS     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TopicGetNG     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TopicAddNoScNG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TopicUniInfoNG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TopicPostNG    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TopicDelNG     </t>
+  </si>
+  <si>
+    <t>"Sn00"  //</t>
+  </si>
+  <si>
+    <t>文章专题创建成功</t>
+  </si>
+  <si>
+    <t>"Sn01"  //</t>
+  </si>
+  <si>
+    <t>文章专题编辑成功</t>
+  </si>
+  <si>
+    <t>"Sn02"  //</t>
+  </si>
+  <si>
+    <t>文章专题删除成功</t>
+  </si>
+  <si>
+    <t>"Fn00"  //</t>
+  </si>
+  <si>
+    <t>文章专题查询失败</t>
+  </si>
+  <si>
+    <t>"F1101" //</t>
+  </si>
+  <si>
+    <t>"Fn01"  //</t>
+  </si>
+  <si>
+    <t>文章专题内文章应当唯一</t>
+  </si>
+  <si>
+    <t>"F404"  //</t>
+  </si>
+  <si>
+    <t>文章专题关联文章同步失败</t>
+  </si>
+  <si>
+    <t>"Fn03"  //</t>
+  </si>
+  <si>
+    <t>文章专题删除</t>
+  </si>
+  <si>
+    <t>TopicAddSS</t>
+  </si>
+  <si>
+    <t>TopicEditSS</t>
+  </si>
+  <si>
+    <t>TopicDelSS</t>
+  </si>
+  <si>
+    <t>TopicGetNG</t>
+  </si>
+  <si>
+    <t>TopicAddNoScNG</t>
+  </si>
+  <si>
+    <t>TopicUniInfoNG</t>
+  </si>
+  <si>
+    <t>TopicPostNG</t>
+  </si>
+  <si>
+    <t>TopicDelNG</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1060,6 +1418,18 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFC77DBB"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1097,7 +1467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1116,6 +1486,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1604,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3957,8 +4331,1085 @@
         <v>163</v>
       </c>
     </row>
+    <row r="79" spans="1:9" ht="17.25">
+      <c r="A79" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="6">
+        <v>9</v>
+      </c>
+      <c r="E79" s="5">
+        <f t="shared" ref="E79:E109" si="3">IF(C79&lt;&gt;C78,0,IF(D79&lt;&gt;D78,0,E78+1))</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="17.25">
+      <c r="A80" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80" s="6">
+        <v>9</v>
+      </c>
+      <c r="E80" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="17.25">
+      <c r="A81" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" s="6">
+        <v>9</v>
+      </c>
+      <c r="E81" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="17.25">
+      <c r="A82" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="6">
+        <v>9</v>
+      </c>
+      <c r="E82" s="5">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="17.25">
+      <c r="A83" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="6">
+        <v>9</v>
+      </c>
+      <c r="E83" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="17.25">
+      <c r="A84" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="6">
+        <v>9</v>
+      </c>
+      <c r="E84" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="17.25">
+      <c r="A85" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="6">
+        <v>9</v>
+      </c>
+      <c r="E85" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="17.25">
+      <c r="A86" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="6">
+        <v>9</v>
+      </c>
+      <c r="E86" s="5">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="17.25">
+      <c r="A87" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="6">
+        <v>9</v>
+      </c>
+      <c r="E87" s="5">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="17.25">
+      <c r="A88" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="6">
+        <v>9</v>
+      </c>
+      <c r="E88" s="5">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="17.25">
+      <c r="A89" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E89" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="17.25">
+      <c r="A90" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E90" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="17.25">
+      <c r="A91" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E91" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="17.25">
+      <c r="A92" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E92" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="17.25">
+      <c r="A93" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E93" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="17.25">
+      <c r="A94" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E94" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="17.25">
+      <c r="A95" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E95" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="17.25">
+      <c r="A96" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E96" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="17.25">
+      <c r="A97" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E97" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="17.25">
+      <c r="A98" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E98" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="17.25">
+      <c r="A99" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E99" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="17.25">
+      <c r="A100" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E100" s="5">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="17.25">
+      <c r="A101" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E101" s="5">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="17.25">
+      <c r="A102" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E102" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="17.25">
+      <c r="A103" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E103" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="17.25">
+      <c r="A104" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E104" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="I104" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="17.25">
+      <c r="A105" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E105" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="17.25">
+      <c r="A106" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E106" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="17.25">
+      <c r="A107" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E107" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="17.25">
+      <c r="A108" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E108" s="5">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="17.25">
+      <c r="A109" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E109" s="5">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C4" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="B7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C7" t="s">
+        <v>437</v>
+      </c>
+      <c r="D7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="B8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C8" t="s">
+        <v>439</v>
+      </c>
+      <c r="D8" t="s">
+        <v>369</v>
+      </c>
+      <c r="E8" t="s">
+        <v>392</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/admin/src/zoom/respCode/response_code.xlsx
+++ b/admin/src/zoom/respCode/response_code.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="437">
   <si>
     <t>ID</t>
   </si>
@@ -101,9 +101,6 @@
     <t>系统异常</t>
   </si>
   <si>
-    <t>System exception</t>
-  </si>
-  <si>
     <t>ValidErr</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>参数非法</t>
   </si>
   <si>
-    <t>Illegal parameters</t>
-  </si>
-  <si>
     <t>LoginErr</t>
   </si>
   <si>
@@ -125,9 +119,6 @@
     <t>尚未登陆</t>
   </si>
   <si>
-    <t>Not logged in yet</t>
-  </si>
-  <si>
     <t>AuthErr</t>
   </si>
   <si>
@@ -137,9 +128,6 @@
     <t>无权访问</t>
   </si>
   <si>
-    <t>No access rights</t>
-  </si>
-  <si>
     <t>PathErr</t>
   </si>
   <si>
@@ -149,243 +137,162 @@
     <t>路径不存在</t>
   </si>
   <si>
-    <t>Path does not exist</t>
-  </si>
-  <si>
     <t>DictAddSS</t>
   </si>
   <si>
     <t>字典创建成功</t>
   </si>
   <si>
-    <t>Dictionary creation successful</t>
-  </si>
-  <si>
     <t>DictEditSS</t>
   </si>
   <si>
     <t>字典编辑成功</t>
   </si>
   <si>
-    <t>Dictionary editing successful</t>
-  </si>
-  <si>
     <t>DictSortSS</t>
   </si>
   <si>
     <t>字典排序成功</t>
   </si>
   <si>
-    <t>Dictionary sorting successful</t>
-  </si>
-  <si>
     <t>DictDelSS</t>
   </si>
   <si>
     <t>字典封存成功</t>
   </si>
   <si>
-    <t>Dictionary sealing successful</t>
-  </si>
-  <si>
     <t>DictGetNG</t>
   </si>
   <si>
     <t>字典查询失败</t>
   </si>
   <si>
-    <t>Dictionary query failed</t>
-  </si>
-  <si>
     <t>DictUniNG</t>
   </si>
   <si>
     <t>字典分组下字典值唯一</t>
   </si>
   <si>
-    <t>Dictionary value is unique under dictionary group</t>
-  </si>
-  <si>
     <t>DictMarkNG</t>
   </si>
   <si>
     <t>内置字典禁止刪除</t>
   </si>
   <si>
-    <t>Built-in dictionary cannot be deleted</t>
-  </si>
-  <si>
     <t>DictSortNG</t>
   </si>
   <si>
     <t>字典排序失败</t>
   </si>
   <si>
-    <t>Dictionary sorting failed</t>
-  </si>
-  <si>
     <t>ResponseAddSS</t>
   </si>
   <si>
     <t>响应码创建成功</t>
   </si>
   <si>
-    <t>Response code creation successful</t>
-  </si>
-  <si>
     <t>ResponseAddSSWNC</t>
   </si>
   <si>
     <t>响应码创建成功,实际响应码为{{code}}</t>
   </si>
   <si>
-    <t>Response code creation successful, actual response code is {{code}}</t>
-  </si>
-  <si>
     <t>ResponseEditSS</t>
   </si>
   <si>
     <t>响应码编辑成功</t>
   </si>
   <si>
-    <t>Response code editing successful</t>
-  </si>
-  <si>
     <t>ResponseDelSS</t>
   </si>
   <si>
     <t>响应码封存成功</t>
   </si>
   <si>
-    <t>Response code sealing successful</t>
-  </si>
-  <si>
     <t>ResponseGetNG</t>
   </si>
   <si>
     <t>响应码查询失败</t>
   </si>
   <si>
-    <t>Response code query failed</t>
-  </si>
-  <si>
     <t>ResponseUniNG</t>
   </si>
   <si>
     <t>响应码全局唯一</t>
   </si>
   <si>
-    <t>Response code is globally unique</t>
-  </si>
-  <si>
     <t>ResponseMarkNG</t>
   </si>
   <si>
     <t>内置响应码禁止删除</t>
   </si>
   <si>
-    <t>Built-in response code cannot be deleted</t>
-  </si>
-  <si>
     <t>RouterAddSS</t>
   </si>
   <si>
     <t>路由创建成功</t>
   </si>
   <si>
-    <t>Route creation successful</t>
-  </si>
-  <si>
     <t>RouterEditSS</t>
   </si>
   <si>
     <t>路由编辑成功</t>
   </si>
   <si>
-    <t>Route editing successful</t>
-  </si>
-  <si>
     <t>RouterDelSS</t>
   </si>
   <si>
     <t>路由删除成功</t>
   </si>
   <si>
-    <t>Route deletion successful</t>
-  </si>
-  <si>
     <t>RouterGetNG</t>
   </si>
   <si>
     <t>路由查询失败</t>
   </si>
   <si>
-    <t>Route query failed</t>
-  </si>
-  <si>
     <t>RouterUniUrlNG</t>
   </si>
   <si>
     <t>路由地址全局唯一</t>
   </si>
   <si>
-    <t>Route address is globally unique</t>
-  </si>
-  <si>
     <t>RouterUniNameNG</t>
   </si>
   <si>
     <t>路由名称全局唯一</t>
   </si>
   <si>
-    <t>Route name is globally unique</t>
-  </si>
-  <si>
     <t>RouterMarkNG</t>
   </si>
   <si>
     <t>内置路由禁止删除</t>
   </si>
   <si>
-    <t>Built-in route cannot be deleted</t>
-  </si>
-  <si>
     <t>RouterDelNG</t>
   </si>
   <si>
     <t>路由删除</t>
   </si>
   <si>
-    <t>Route deletion</t>
-  </si>
-  <si>
     <t>PermissionAddSS</t>
   </si>
   <si>
     <t>权限创建成功</t>
   </si>
   <si>
-    <t>Permission creation successful</t>
-  </si>
-  <si>
     <t>PermissionEditSS</t>
   </si>
   <si>
     <t>权限编辑成功</t>
   </si>
   <si>
-    <t>Permission editing successful</t>
-  </si>
-  <si>
     <t>PermissionDelSS</t>
   </si>
   <si>
     <t>权限删除成功</t>
   </si>
   <si>
-    <t>Permission deletion successful</t>
-  </si>
-  <si>
     <t>PermissionSortSS</t>
   </si>
   <si>
@@ -395,54 +302,36 @@
     <t>权限查询失败</t>
   </si>
   <si>
-    <t>Permission query failed</t>
-  </si>
-  <si>
     <t>PermissionUniAliasNG</t>
   </si>
   <si>
     <t>权限别名全局唯一</t>
   </si>
   <si>
-    <t>Permission alias is globally unique</t>
-  </si>
-  <si>
     <t>PermissionUniNameNG</t>
   </si>
   <si>
     <t>权限名称全局唯一</t>
   </si>
   <si>
-    <t>Permission name is globally unique</t>
-  </si>
-  <si>
     <t>PermissionMarkNG</t>
   </si>
   <si>
     <t>内置权限禁止删除</t>
   </si>
   <si>
-    <t>Built-in permission cannot be deleted</t>
-  </si>
-  <si>
     <t>PermissionRouterNG</t>
   </si>
   <si>
     <t>权限配置路由同步失败</t>
   </si>
   <si>
-    <t>Permission configuration route synchronization failed</t>
-  </si>
-  <si>
     <t>PermissionDelNG</t>
   </si>
   <si>
     <t>权限配置删除失败</t>
   </si>
   <si>
-    <t>Permission configuration deletion failed</t>
-  </si>
-  <si>
     <t>RoleAddSS</t>
   </si>
   <si>
@@ -452,81 +341,54 @@
     <t>角色创建成功</t>
   </si>
   <si>
-    <t>Role creation successful</t>
-  </si>
-  <si>
     <t>RoleEditSS</t>
   </si>
   <si>
     <t>角色编辑成功</t>
   </si>
   <si>
-    <t>Role editing successful</t>
-  </si>
-  <si>
     <t>RoleDelSS</t>
   </si>
   <si>
     <t>角色删除失败</t>
   </si>
   <si>
-    <t>Role deletion failed</t>
-  </si>
-  <si>
     <t>RoleGetNG</t>
   </si>
   <si>
     <t>角色查询失败</t>
   </si>
   <si>
-    <t>Role query failed</t>
-  </si>
-  <si>
     <t>RoleMarkNG</t>
   </si>
   <si>
     <t>内置角色禁止编辑</t>
   </si>
   <si>
-    <t>Built-in roles cannot be edited</t>
-  </si>
-  <si>
     <t>RoleNameUniNG</t>
   </si>
   <si>
     <t>角色名全局唯一</t>
   </si>
   <si>
-    <t>Role name is globally unique</t>
-  </si>
-  <si>
     <t>RolePermissionNG</t>
   </si>
   <si>
     <t>角色权限配置失败</t>
   </si>
   <si>
-    <t>Role permission configuration failed</t>
-  </si>
-  <si>
     <t>SysConfigEditSS</t>
   </si>
   <si>
     <t>系统配置编辑成功</t>
   </si>
   <si>
-    <t>System configuration editing successful</t>
-  </si>
-  <si>
     <t>SysConfigGetNG</t>
   </si>
   <si>
     <t>系统配置查询失败</t>
   </si>
   <si>
-    <t>System configuration query failed</t>
-  </si>
-  <si>
     <t>DeptAddSS</t>
   </si>
   <si>
@@ -602,42 +464,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Department created successfully</t>
-  </si>
-  <si>
-    <t>Department editing successful</t>
-  </si>
-  <si>
-    <t>Department deleted successfully</t>
-  </si>
-  <si>
-    <t>Department sorting successful</t>
-  </si>
-  <si>
-    <t>Department migration successful</t>
-  </si>
-  <si>
-    <t>Department query failed</t>
-  </si>
-  <si>
-    <t>Department name Globally unique</t>
-  </si>
-  <si>
-    <t>Deletion of built-in departments is prohibited</t>
-  </si>
-  <si>
-    <t>Department deletion failed</t>
-  </si>
-  <si>
-    <t>Department has sub-departments and is prohibited from deletion</t>
-  </si>
-  <si>
-    <t>Department members cannot be deleted if they exist</t>
-  </si>
-  <si>
-    <t>Department migration failed</t>
-  </si>
-  <si>
     <t>AccountAddSS</t>
   </si>
   <si>
@@ -734,45 +560,12 @@
     <t>登陆账号全局唯一</t>
   </si>
   <si>
-    <t>Login account created successfully</t>
-  </si>
-  <si>
-    <t>Login account edited successfully</t>
-  </si>
-  <si>
-    <t>Login account deleted successfully</t>
-  </si>
-  <si>
-    <t>Login account reset successfully</t>
-  </si>
-  <si>
-    <t>Login account query failed</t>
-  </si>
-  <si>
-    <t>Login account is globally unique</t>
-  </si>
-  <si>
-    <t>Account role synchronization failed</t>
-  </si>
-  <si>
-    <t>Editing of special accounts is prohibited</t>
-  </si>
-  <si>
-    <t>Login account deletion failed</t>
-  </si>
-  <si>
-    <t>Login account reset failed</t>
-  </si>
-  <si>
     <t>RoleDelNG</t>
   </si>
   <si>
     <t>权限排序成功</t>
   </si>
   <si>
-    <t>Permissions sorted successfully</t>
-  </si>
-  <si>
     <t>AuthLoginSS</t>
   </si>
   <si>
@@ -1025,27 +818,6 @@
     <t>77</t>
   </si>
   <si>
-    <t>Processed successfully</t>
-  </si>
-  <si>
-    <t>Landed successfully</t>
-  </si>
-  <si>
-    <t>Password reset successful</t>
-  </si>
-  <si>
-    <t>Processing failed</t>
-  </si>
-  <si>
-    <t>Login failed, please contact the administrator</t>
-  </si>
-  <si>
-    <t>Abnormal login, please contact the administrator</t>
-  </si>
-  <si>
-    <t>Password reset failed, please contact the administrator</t>
-  </si>
-  <si>
     <t>CategoryAddSS</t>
   </si>
   <si>
@@ -1142,9 +914,6 @@
     <t>SourceAddSS</t>
   </si>
   <si>
-    <t>//</t>
-  </si>
-  <si>
     <t>资源配置表创建成功</t>
   </si>
   <si>
@@ -1232,9 +1001,6 @@
     <t>标签地址全局唯一</t>
   </si>
   <si>
-    <t>文章标签下存在数据禁止删除</t>
-  </si>
-  <si>
     <t>TagDelNG</t>
   </si>
   <si>
@@ -1286,72 +1052,24 @@
     <t>TagDelPostNG</t>
   </si>
   <si>
-    <t xml:space="preserve">TopicAddSS     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TopicEditSS    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TopicDelSS     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TopicGetNG     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TopicAddNoScNG </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TopicUniInfoNG </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TopicPostNG    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TopicDelNG     </t>
-  </si>
-  <si>
-    <t>"Sn00"  //</t>
-  </si>
-  <si>
     <t>文章专题创建成功</t>
   </si>
   <si>
-    <t>"Sn01"  //</t>
-  </si>
-  <si>
     <t>文章专题编辑成功</t>
   </si>
   <si>
-    <t>"Sn02"  //</t>
-  </si>
-  <si>
     <t>文章专题删除成功</t>
   </si>
   <si>
-    <t>"Fn00"  //</t>
-  </si>
-  <si>
     <t>文章专题查询失败</t>
   </si>
   <si>
-    <t>"F1101" //</t>
-  </si>
-  <si>
-    <t>"Fn01"  //</t>
-  </si>
-  <si>
     <t>文章专题内文章应当唯一</t>
   </si>
   <si>
-    <t>"F404"  //</t>
-  </si>
-  <si>
     <t>文章专题关联文章同步失败</t>
   </si>
   <si>
-    <t>"Fn03"  //</t>
-  </si>
-  <si>
     <t>文章专题删除</t>
   </si>
   <si>
@@ -1401,6 +1119,231 @@
   </si>
   <si>
     <t>108</t>
+  </si>
+  <si>
+    <t>PostAddSS</t>
+  </si>
+  <si>
+    <t>文章或页面创建成功</t>
+  </si>
+  <si>
+    <t>PostEditSS</t>
+  </si>
+  <si>
+    <t>文章或页面编辑成功</t>
+  </si>
+  <si>
+    <t>PostGetNG</t>
+  </si>
+  <si>
+    <t>文章或页面查询失败</t>
+  </si>
+  <si>
+    <t>PostAddNoScNG</t>
+  </si>
+  <si>
+    <t>文章或页面必须有主图</t>
+  </si>
+  <si>
+    <t>PostTagNG</t>
+  </si>
+  <si>
+    <t>文章关联标签更新失败</t>
+  </si>
+  <si>
+    <t>PostSourceNG</t>
+  </si>
+  <si>
+    <t>文章关联资源更新失败</t>
+  </si>
+  <si>
+    <t>PostMoreNG</t>
+  </si>
+  <si>
+    <t>文章关联详情更新失败</t>
+  </si>
+  <si>
+    <t>PostUniXxxNG</t>
+  </si>
+  <si>
+    <t>文章或页面地址全局唯一</t>
+  </si>
+  <si>
+    <t>PostMoreUniXxxNG</t>
+  </si>
+  <si>
+    <t>文章关联地址全局唯一</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BannerAddSS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BannerEditSS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BannerAddNoScNG </t>
+  </si>
+  <si>
+    <t>BannerDelSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BannerGetNG </t>
+  </si>
+  <si>
+    <t>BannerUniXxxNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BannerDelNG </t>
+  </si>
+  <si>
+    <t>Banner创建成功</t>
+  </si>
+  <si>
+    <t>Banner编辑成功</t>
+  </si>
+  <si>
+    <t>Banner删除成功</t>
+  </si>
+  <si>
+    <t>Banner查询失败</t>
+  </si>
+  <si>
+    <t>Banner未提交图片</t>
+  </si>
+  <si>
+    <t>Banner地址全局唯一</t>
+  </si>
+  <si>
+    <t>Banner删除失败</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>评论更新成功</t>
+  </si>
+  <si>
+    <t>评论查询失败</t>
+  </si>
+  <si>
+    <t>PostCommentEditSS</t>
+  </si>
+  <si>
+    <t>PostCommentGetNG</t>
+  </si>
+  <si>
+    <t>LinksAddSS</t>
+  </si>
+  <si>
+    <t>友情链接创建成功</t>
+  </si>
+  <si>
+    <t>LinksEditSS</t>
+  </si>
+  <si>
+    <t>友情链接编辑成功</t>
+  </si>
+  <si>
+    <t>LinksDelSS</t>
+  </si>
+  <si>
+    <t>友情链接删除成功</t>
+  </si>
+  <si>
+    <t>LinksGetNG</t>
+  </si>
+  <si>
+    <t>友情链接查询失败</t>
+  </si>
+  <si>
+    <t>LinksAddNoScNG</t>
+  </si>
+  <si>
+    <t>友情链接未提交图片</t>
+  </si>
+  <si>
+    <t>LinksUniXxxNG</t>
+  </si>
+  <si>
+    <t>友情链接地址全局唯一</t>
+  </si>
+  <si>
+    <t>LinksDelNG</t>
+  </si>
+  <si>
+    <t>友情链接删除失败</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>133</t>
   </si>
 </sst>
 </file>
@@ -1978,17 +1921,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="24.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="10.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" style="1" customWidth="1"/>
     <col min="7" max="8" width="43.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="82.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -2048,15 +1991,15 @@
         <v>21</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="17.25">
       <c r="A3" s="4" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>19</v>
@@ -2072,21 +2015,21 @@
         <v>11</v>
       </c>
       <c r="G3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="I3" s="4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="17.25">
       <c r="A4" s="4" t="s">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>19</v>
@@ -2102,21 +2045,21 @@
         <v>11</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25">
       <c r="A5" s="4" t="s">
-        <v>258</v>
+        <v>189</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>19</v>
@@ -2132,21 +2075,21 @@
         <v>11</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.25">
       <c r="A6" s="4" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>19</v>
@@ -2162,18 +2105,18 @@
         <v>11</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17.25">
       <c r="A7" s="4" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>9</v>
@@ -2198,15 +2141,15 @@
         <v>13</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17.25">
       <c r="A8" s="4" t="s">
-        <v>259</v>
+        <v>190</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>246</v>
+        <v>177</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>10</v>
@@ -2222,21 +2165,21 @@
         <v>11</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>248</v>
+        <v>179</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>248</v>
+        <v>179</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>331</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25">
       <c r="A9" s="4" t="s">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>247</v>
+        <v>178</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>10</v>
@@ -2252,18 +2195,18 @@
         <v>11</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>249</v>
+        <v>180</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>249</v>
+        <v>180</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.25">
       <c r="A10" s="4" t="s">
-        <v>261</v>
+        <v>192</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>14</v>
@@ -2288,15 +2231,15 @@
         <v>17</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>333</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="17.25">
       <c r="A11" s="4" t="s">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>15</v>
@@ -2312,21 +2255,21 @@
         <v>11</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>251</v>
+        <v>182</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>251</v>
+        <v>182</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>334</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17.25">
       <c r="A12" s="4" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>15</v>
@@ -2342,21 +2285,21 @@
         <v>11</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>252</v>
+        <v>183</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>252</v>
+        <v>183</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>335</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17.25">
       <c r="A13" s="4" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>15</v>
@@ -2372,21 +2315,21 @@
         <v>11</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>253</v>
+        <v>184</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>253</v>
+        <v>184</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>336</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.25">
       <c r="A14" s="4" t="s">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>10</v>
@@ -2402,21 +2345,21 @@
         <v>11</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.25">
       <c r="A15" s="4" t="s">
-        <v>266</v>
+        <v>197</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>10</v>
@@ -2432,21 +2375,21 @@
         <v>11</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17.25">
       <c r="A16" s="4" t="s">
-        <v>267</v>
+        <v>198</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>10</v>
@@ -2462,21 +2405,21 @@
         <v>11</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.25">
       <c r="A17" s="4" t="s">
-        <v>268</v>
+        <v>199</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>10</v>
@@ -2492,21 +2435,21 @@
         <v>11</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.25">
       <c r="A18" s="4" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>15</v>
@@ -2522,21 +2465,21 @@
         <v>11</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.25">
       <c r="A19" s="4" t="s">
-        <v>270</v>
+        <v>201</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>15</v>
@@ -2552,21 +2495,21 @@
         <v>11</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="17.25">
       <c r="A20" s="4" t="s">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>15</v>
@@ -2582,21 +2525,21 @@
         <v>11</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.25">
       <c r="A21" s="4" t="s">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>15</v>
@@ -2612,21 +2555,21 @@
         <v>11</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17.25">
       <c r="A22" s="4" t="s">
-        <v>273</v>
+        <v>204</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>10</v>
@@ -2642,21 +2585,21 @@
         <v>11</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17.25">
       <c r="A23" s="4" t="s">
-        <v>274</v>
+        <v>205</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>10</v>
@@ -2672,21 +2615,21 @@
         <v>11</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.25">
       <c r="A24" s="4" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>10</v>
@@ -2702,21 +2645,21 @@
         <v>11</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="17.25">
       <c r="A25" s="4" t="s">
-        <v>276</v>
+        <v>207</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>10</v>
@@ -2732,21 +2675,21 @@
         <v>11</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.25">
       <c r="A26" s="4" t="s">
-        <v>277</v>
+        <v>208</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>15</v>
@@ -2762,21 +2705,21 @@
         <v>11</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="17.25">
       <c r="A27" s="4" t="s">
-        <v>278</v>
+        <v>209</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>15</v>
@@ -2792,21 +2735,21 @@
         <v>11</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17.25">
       <c r="A28" s="4" t="s">
-        <v>279</v>
+        <v>210</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>15</v>
@@ -2822,21 +2765,21 @@
         <v>11</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="17.25">
       <c r="A29" s="4" t="s">
-        <v>280</v>
+        <v>211</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>10</v>
@@ -2852,21 +2795,21 @@
         <v>11</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25">
       <c r="A30" s="4" t="s">
-        <v>281</v>
+        <v>212</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>10</v>
@@ -2882,21 +2825,21 @@
         <v>11</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17.25">
       <c r="A31" s="4" t="s">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>10</v>
@@ -2912,21 +2855,21 @@
         <v>11</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="17.25">
       <c r="A32" s="4" t="s">
-        <v>283</v>
+        <v>214</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>15</v>
@@ -2942,21 +2885,21 @@
         <v>11</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="17.25">
       <c r="A33" s="4" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>15</v>
@@ -2972,21 +2915,21 @@
         <v>11</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="17.25">
       <c r="A34" s="4" t="s">
-        <v>285</v>
+        <v>216</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>15</v>
@@ -3002,21 +2945,21 @@
         <v>11</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="17.25">
       <c r="A35" s="4" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>15</v>
@@ -3032,21 +2975,21 @@
         <v>11</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="17.25">
       <c r="A36" s="4" t="s">
-        <v>287</v>
+        <v>218</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>15</v>
@@ -3062,21 +3005,21 @@
         <v>11</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="17.25">
       <c r="A37" s="4" t="s">
-        <v>288</v>
+        <v>219</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>10</v>
@@ -3092,21 +3035,21 @@
         <v>11</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="17.25">
       <c r="A38" s="4" t="s">
-        <v>289</v>
+        <v>220</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>10</v>
@@ -3122,21 +3065,21 @@
         <v>11</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="17.25">
       <c r="A39" s="4" t="s">
-        <v>290</v>
+        <v>221</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>10</v>
@@ -3152,21 +3095,21 @@
         <v>11</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="17.25">
       <c r="A40" s="4" t="s">
-        <v>291</v>
+        <v>222</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>10</v>
@@ -3182,21 +3125,21 @@
         <v>11</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>245</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="17.25">
       <c r="A41" s="4" t="s">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>15</v>
@@ -3212,21 +3155,21 @@
         <v>11</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="17.25">
       <c r="A42" s="4" t="s">
-        <v>293</v>
+        <v>224</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>15</v>
@@ -3242,21 +3185,21 @@
         <v>11</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="17.25">
       <c r="A43" s="4" t="s">
-        <v>294</v>
+        <v>225</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>15</v>
@@ -3272,21 +3215,21 @@
         <v>11</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="17.25">
       <c r="A44" s="4" t="s">
-        <v>295</v>
+        <v>226</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>15</v>
@@ -3302,21 +3245,21 @@
         <v>11</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="17.25">
       <c r="A45" s="4" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>15</v>
@@ -3332,21 +3275,21 @@
         <v>11</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="17.25">
       <c r="A46" s="4" t="s">
-        <v>297</v>
+        <v>228</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>15</v>
@@ -3362,27 +3305,27 @@
         <v>11</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="17.25">
       <c r="A47" s="4" t="s">
-        <v>298</v>
+        <v>229</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E47" s="5">
         <f t="shared" si="1"/>
@@ -3392,27 +3335,27 @@
         <v>11</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>139</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17.25">
       <c r="A48" s="4" t="s">
-        <v>299</v>
+        <v>230</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E48" s="5">
         <f t="shared" si="1"/>
@@ -3422,27 +3365,27 @@
         <v>11</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="17.25">
       <c r="A49" s="4" t="s">
-        <v>300</v>
+        <v>231</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E49" s="5">
         <f t="shared" si="1"/>
@@ -3452,27 +3395,27 @@
         <v>11</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>145</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="17.25">
       <c r="A50" s="4" t="s">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E50" s="5">
         <f t="shared" si="1"/>
@@ -3482,27 +3425,27 @@
         <v>11</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="17.25">
       <c r="A51" s="4" t="s">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E51" s="5">
         <f t="shared" si="1"/>
@@ -3512,27 +3455,27 @@
         <v>11</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>151</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="17.25">
       <c r="A52" s="4" t="s">
-        <v>303</v>
+        <v>234</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E52" s="5">
         <f t="shared" si="1"/>
@@ -3542,27 +3485,27 @@
         <v>11</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>154</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="17.25">
       <c r="A53" s="4" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E53" s="5">
         <f t="shared" si="1"/>
@@ -3572,27 +3515,27 @@
         <v>11</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="17.25">
       <c r="A54" s="4" t="s">
-        <v>305</v>
+        <v>236</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E54" s="5">
         <f t="shared" si="1"/>
@@ -3602,27 +3545,27 @@
         <v>11</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>145</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="17.25">
       <c r="A55" s="4" t="s">
-        <v>306</v>
+        <v>237</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E55" s="5">
         <f t="shared" si="1"/>
@@ -3632,27 +3575,27 @@
         <v>11</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>189</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="17.25">
       <c r="A56" s="4" t="s">
-        <v>307</v>
+        <v>238</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E56" s="5">
         <f t="shared" si="1"/>
@@ -3662,27 +3605,27 @@
         <v>11</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="17.25">
       <c r="A57" s="4" t="s">
-        <v>308</v>
+        <v>239</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E57" s="5">
         <f t="shared" si="1"/>
@@ -3692,27 +3635,27 @@
         <v>11</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="17.25">
       <c r="A58" s="4" t="s">
-        <v>309</v>
+        <v>240</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E58" s="5">
         <f t="shared" si="1"/>
@@ -3722,27 +3665,27 @@
         <v>11</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>192</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="17.25">
       <c r="A59" s="4" t="s">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E59" s="5">
         <f t="shared" si="1"/>
@@ -3752,27 +3695,27 @@
         <v>11</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="17.25">
       <c r="A60" s="4" t="s">
-        <v>311</v>
+        <v>242</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E60" s="5">
         <f t="shared" si="1"/>
@@ -3782,27 +3725,27 @@
         <v>11</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="17.25">
       <c r="A61" s="4" t="s">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E61" s="5">
         <f t="shared" si="1"/>
@@ -3812,27 +3755,27 @@
         <v>11</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>217</v>
+        <v>159</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>195</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="17.25">
       <c r="A62" s="4" t="s">
-        <v>313</v>
+        <v>244</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E62" s="5">
         <f t="shared" si="1"/>
@@ -3842,27 +3785,27 @@
         <v>11</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="17.25">
       <c r="A63" s="4" t="s">
-        <v>314</v>
+        <v>245</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E63" s="5">
         <f t="shared" si="1"/>
@@ -3872,27 +3815,27 @@
         <v>11</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>197</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="17.25">
       <c r="A64" s="4" t="s">
-        <v>315</v>
+        <v>246</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E64" s="5">
         <f t="shared" si="1"/>
@@ -3902,27 +3845,27 @@
         <v>11</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>198</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="17.25">
       <c r="A65" s="4" t="s">
-        <v>316</v>
+        <v>247</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E65" s="5">
         <f t="shared" si="1"/>
@@ -3932,27 +3875,27 @@
         <v>11</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>199</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="17.25">
       <c r="A66" s="4" t="s">
-        <v>317</v>
+        <v>248</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="E66" s="5">
         <f t="shared" si="1"/>
@@ -3962,21 +3905,21 @@
         <v>11</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>200</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="17.25">
       <c r="A67" s="4" t="s">
-        <v>318</v>
+        <v>249</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>10</v>
@@ -3992,21 +3935,21 @@
         <v>11</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>223</v>
+        <v>165</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>223</v>
+        <v>165</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>233</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="17.25">
       <c r="A68" s="4" t="s">
-        <v>319</v>
+        <v>250</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>10</v>
@@ -4022,21 +3965,21 @@
         <v>11</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>224</v>
+        <v>166</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>224</v>
+        <v>166</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>234</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="17.25">
       <c r="A69" s="4" t="s">
-        <v>320</v>
+        <v>251</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>10</v>
@@ -4052,21 +3995,21 @@
         <v>11</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>235</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="17.25">
       <c r="A70" s="4" t="s">
-        <v>321</v>
+        <v>252</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>10</v>
@@ -4082,21 +4025,21 @@
         <v>11</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>236</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="17.25">
       <c r="A71" s="4" t="s">
-        <v>322</v>
+        <v>253</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>15</v>
@@ -4112,21 +4055,21 @@
         <v>11</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>237</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="17.25">
       <c r="A72" s="4" t="s">
-        <v>323</v>
+        <v>254</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>206</v>
+        <v>148</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>15</v>
@@ -4142,21 +4085,21 @@
         <v>11</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>238</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="17.25">
       <c r="A73" s="4" t="s">
-        <v>324</v>
+        <v>255</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>15</v>
@@ -4172,21 +4115,21 @@
         <v>11</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>239</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="17.25">
       <c r="A74" s="4" t="s">
-        <v>325</v>
+        <v>256</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>15</v>
@@ -4202,21 +4145,21 @@
         <v>11</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>240</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="17.25">
       <c r="A75" s="4" t="s">
-        <v>326</v>
+        <v>257</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>209</v>
+        <v>151</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>15</v>
@@ -4232,21 +4175,21 @@
         <v>11</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>241</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="17.25">
       <c r="A76" s="4" t="s">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>15</v>
@@ -4262,21 +4205,21 @@
         <v>11</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>242</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="17.25">
       <c r="A77" s="4" t="s">
-        <v>328</v>
+        <v>259</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>10</v>
@@ -4292,21 +4235,21 @@
         <v>11</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="17.25">
       <c r="A78" s="4" t="s">
-        <v>329</v>
+        <v>260</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>15</v>
@@ -4322,21 +4265,21 @@
         <v>11</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="17.25">
       <c r="A79" s="4" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>337</v>
+        <v>261</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>10</v>
@@ -4345,17 +4288,17 @@
         <v>9</v>
       </c>
       <c r="E79" s="5">
-        <f t="shared" ref="E79:E109" si="3">IF(C79&lt;&gt;C78,0,IF(D79&lt;&gt;D78,0,E78+1))</f>
+        <f t="shared" ref="E79:E127" si="3">IF(C79&lt;&gt;C78,0,IF(D79&lt;&gt;D78,0,E78+1))</f>
         <v>0</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>19</v>
@@ -4363,10 +4306,10 @@
     </row>
     <row r="80" spans="1:9" ht="17.25">
       <c r="A80" s="4" t="s">
-        <v>359</v>
+        <v>283</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>10</v>
@@ -4379,13 +4322,13 @@
         <v>1</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>348</v>
+        <v>272</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>348</v>
+        <v>272</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>19</v>
@@ -4393,10 +4336,10 @@
     </row>
     <row r="81" spans="1:9" ht="17.25">
       <c r="A81" s="4" t="s">
-        <v>360</v>
+        <v>284</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>339</v>
+        <v>263</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>10</v>
@@ -4409,13 +4352,13 @@
         <v>2</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>349</v>
+        <v>273</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>349</v>
+        <v>273</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>19</v>
@@ -4423,10 +4366,10 @@
     </row>
     <row r="82" spans="1:9" ht="17.25">
       <c r="A82" s="4" t="s">
-        <v>361</v>
+        <v>285</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>340</v>
+        <v>264</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>10</v>
@@ -4439,13 +4382,13 @@
         <v>3</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>19</v>
@@ -4453,10 +4396,10 @@
     </row>
     <row r="83" spans="1:9" ht="17.25">
       <c r="A83" s="4" t="s">
-        <v>362</v>
+        <v>286</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>341</v>
+        <v>265</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>15</v>
@@ -4469,13 +4412,13 @@
         <v>0</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>19</v>
@@ -4483,10 +4426,10 @@
     </row>
     <row r="84" spans="1:9" ht="17.25">
       <c r="A84" s="4" t="s">
-        <v>363</v>
+        <v>287</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>342</v>
+        <v>266</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>15</v>
@@ -4499,13 +4442,13 @@
         <v>1</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>352</v>
+        <v>276</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>352</v>
+        <v>276</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>19</v>
@@ -4513,10 +4456,10 @@
     </row>
     <row r="85" spans="1:9" ht="17.25">
       <c r="A85" s="4" t="s">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>343</v>
+        <v>267</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>15</v>
@@ -4529,13 +4472,13 @@
         <v>2</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>19</v>
@@ -4543,10 +4486,10 @@
     </row>
     <row r="86" spans="1:9" ht="17.25">
       <c r="A86" s="4" t="s">
-        <v>365</v>
+        <v>289</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>344</v>
+        <v>268</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>15</v>
@@ -4559,13 +4502,13 @@
         <v>3</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>354</v>
+        <v>278</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>354</v>
+        <v>278</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>19</v>
@@ -4573,10 +4516,10 @@
     </row>
     <row r="87" spans="1:9" ht="17.25">
       <c r="A87" s="4" t="s">
-        <v>366</v>
+        <v>290</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>15</v>
@@ -4589,13 +4532,13 @@
         <v>4</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>19</v>
@@ -4603,10 +4546,10 @@
     </row>
     <row r="88" spans="1:9" ht="17.25">
       <c r="A88" s="4" t="s">
-        <v>367</v>
+        <v>291</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>346</v>
+        <v>270</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>15</v>
@@ -4619,13 +4562,13 @@
         <v>5</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>355</v>
+        <v>279</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>355</v>
+        <v>279</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>19</v>
@@ -4633,29 +4576,29 @@
     </row>
     <row r="89" spans="1:9" ht="17.25">
       <c r="A89" s="4" t="s">
-        <v>382</v>
+        <v>305</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>368</v>
+        <v>292</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="E89" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>370</v>
+        <v>293</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>379</v>
+        <v>302</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>19</v>
@@ -4663,29 +4606,29 @@
     </row>
     <row r="90" spans="1:9" ht="17.25">
       <c r="A90" s="4" t="s">
-        <v>383</v>
+        <v>306</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>371</v>
+        <v>294</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="E90" s="5">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>372</v>
+        <v>295</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>380</v>
+        <v>303</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>19</v>
@@ -4693,29 +4636,29 @@
     </row>
     <row r="91" spans="1:9" ht="17.25">
       <c r="A91" s="4" t="s">
-        <v>384</v>
+        <v>307</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>373</v>
+        <v>296</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="E91" s="5">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>374</v>
+        <v>297</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>374</v>
+        <v>297</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>19</v>
@@ -4723,29 +4666,29 @@
     </row>
     <row r="92" spans="1:9" ht="17.25">
       <c r="A92" s="4" t="s">
-        <v>385</v>
+        <v>308</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>375</v>
+        <v>298</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="E92" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>376</v>
+        <v>299</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>381</v>
+        <v>304</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>19</v>
@@ -4753,29 +4696,29 @@
     </row>
     <row r="93" spans="1:9" ht="17.25">
       <c r="A93" s="4" t="s">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>377</v>
+        <v>300</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="E93" s="5">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>378</v>
+        <v>301</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>378</v>
+        <v>301</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>19</v>
@@ -4783,29 +4726,29 @@
     </row>
     <row r="94" spans="1:9" ht="17.25">
       <c r="A94" s="4" t="s">
-        <v>407</v>
+        <v>329</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>387</v>
+        <v>310</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E94" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>388</v>
+        <v>311</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>401</v>
+        <v>323</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>19</v>
@@ -4813,29 +4756,29 @@
     </row>
     <row r="95" spans="1:9" ht="17.25">
       <c r="A95" s="4" t="s">
-        <v>408</v>
+        <v>330</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>389</v>
+        <v>312</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E95" s="5">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>390</v>
+        <v>313</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>19</v>
@@ -4843,29 +4786,29 @@
     </row>
     <row r="96" spans="1:9" ht="17.25">
       <c r="A96" s="4" t="s">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>391</v>
+        <v>314</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E96" s="5">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>392</v>
+        <v>315</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>403</v>
+        <v>325</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>19</v>
@@ -4873,29 +4816,29 @@
     </row>
     <row r="97" spans="1:9" ht="17.25">
       <c r="A97" s="4" t="s">
-        <v>410</v>
+        <v>332</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>393</v>
+        <v>316</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E97" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>394</v>
+        <v>317</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>404</v>
+        <v>326</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>19</v>
@@ -4903,29 +4846,29 @@
     </row>
     <row r="98" spans="1:9" ht="17.25">
       <c r="A98" s="4" t="s">
-        <v>411</v>
+        <v>333</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>395</v>
+        <v>318</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E98" s="5">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>396</v>
+        <v>319</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>396</v>
+        <v>319</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>19</v>
@@ -4933,29 +4876,29 @@
     </row>
     <row r="99" spans="1:9" ht="17.25">
       <c r="A99" s="4" t="s">
-        <v>412</v>
+        <v>334</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>397</v>
+        <v>320</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E99" s="5">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>398</v>
+        <v>321</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>405</v>
+        <v>327</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>19</v>
@@ -4963,29 +4906,29 @@
     </row>
     <row r="100" spans="1:9" ht="17.25">
       <c r="A100" s="4" t="s">
-        <v>413</v>
+        <v>335</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>416</v>
+        <v>338</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E100" s="5">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>415</v>
+        <v>337</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>415</v>
+        <v>337</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>19</v>
@@ -4993,29 +4936,29 @@
     </row>
     <row r="101" spans="1:9" ht="17.25">
       <c r="A101" s="4" t="s">
-        <v>414</v>
+        <v>336</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>400</v>
+        <v>322</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E101" s="5">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>392</v>
+        <v>315</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>406</v>
+        <v>328</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>19</v>
@@ -5023,29 +4966,29 @@
     </row>
     <row r="102" spans="1:9" ht="17.25">
       <c r="A102" s="4" t="s">
-        <v>448</v>
+        <v>354</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>440</v>
+        <v>346</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="E102" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>426</v>
+        <v>339</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>426</v>
+        <v>339</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>19</v>
@@ -5053,29 +4996,29 @@
     </row>
     <row r="103" spans="1:9" ht="17.25">
       <c r="A103" s="4" t="s">
-        <v>449</v>
+        <v>355</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>441</v>
+        <v>347</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="E103" s="5">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>428</v>
+        <v>340</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>428</v>
+        <v>340</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>19</v>
@@ -5083,29 +5026,29 @@
     </row>
     <row r="104" spans="1:9" ht="17.25">
       <c r="A104" s="4" t="s">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>442</v>
+        <v>348</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="E104" s="5">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>430</v>
+        <v>341</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>430</v>
+        <v>341</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>19</v>
@@ -5113,29 +5056,29 @@
     </row>
     <row r="105" spans="1:9" ht="17.25">
       <c r="A105" s="4" t="s">
-        <v>451</v>
+        <v>357</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>443</v>
+        <v>349</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="E105" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>432</v>
+        <v>342</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>432</v>
+        <v>342</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>19</v>
@@ -5143,29 +5086,29 @@
     </row>
     <row r="106" spans="1:9" ht="17.25">
       <c r="A106" s="4" t="s">
-        <v>452</v>
+        <v>358</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>444</v>
+        <v>350</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="E106" s="5">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>396</v>
+        <v>319</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>396</v>
+        <v>319</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>19</v>
@@ -5173,29 +5116,29 @@
     </row>
     <row r="107" spans="1:9" ht="17.25">
       <c r="A107" s="4" t="s">
-        <v>453</v>
+        <v>359</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>445</v>
+        <v>351</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="E107" s="5">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>435</v>
+        <v>343</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>435</v>
+        <v>343</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>19</v>
@@ -5203,29 +5146,29 @@
     </row>
     <row r="108" spans="1:9" ht="17.25">
       <c r="A108" s="4" t="s">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>446</v>
+        <v>352</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="E108" s="5">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>437</v>
+        <v>344</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>437</v>
+        <v>344</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>19</v>
@@ -5233,31 +5176,781 @@
     </row>
     <row r="109" spans="1:9" ht="17.25">
       <c r="A109" s="4" t="s">
-        <v>455</v>
+        <v>361</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>447</v>
+        <v>353</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="E109" s="5">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>439</v>
+        <v>345</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>439</v>
+        <v>345</v>
       </c>
       <c r="I109" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="17.25">
+      <c r="A110" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E110" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="17.25">
+      <c r="A111" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E111" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="17.25">
+      <c r="A112" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E112" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="17.25">
+      <c r="A113" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E113" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="17.25">
+      <c r="A114" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E114" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="17.25">
+      <c r="A115" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E115" s="5">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="17.25">
+      <c r="A116" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E116" s="5">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="17.25">
+      <c r="A117" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E117" s="5">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="17.25">
+      <c r="A118" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E118" s="5">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="17.25">
+      <c r="A119" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E119" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="17.25">
+      <c r="A120" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E120" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="17.25">
+      <c r="A121" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E121" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="17.25">
+      <c r="A122" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E122" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="17.25">
+      <c r="A123" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E123" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="17.25">
+      <c r="A124" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E124" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="17.25">
+      <c r="A125" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E125" s="5">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="17.25">
+      <c r="A126" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E126" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="17.25">
+      <c r="A127" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E127" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="17.25">
+      <c r="A128" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E128" s="5">
+        <f t="shared" ref="E128:E134" si="4">IF(C128&lt;&gt;C127,0,IF(D128&lt;&gt;D127,0,E127+1))</f>
+        <v>0</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G128" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="I128" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="17.25">
+      <c r="A129" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E129" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="17.25">
+      <c r="A130" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E130" s="5">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G130" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="17.25">
+      <c r="A131" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E131" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="17.25">
+      <c r="A132" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E132" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="17.25">
+      <c r="A133" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E133" s="5">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="17.25">
+      <c r="A134" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E134" s="5">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G134" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="I134" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5269,144 +5962,102 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="41.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E1" t="s">
         <v>417</v>
-      </c>
-      <c r="B1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C1" t="s">
-        <v>426</v>
-      </c>
-      <c r="D1" t="s">
-        <v>369</v>
-      </c>
-      <c r="E1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="B2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D2" t="s">
-        <v>369</v>
-      </c>
       <c r="E2" t="s">
-        <v>390</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="B3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C3" t="s">
-        <v>430</v>
-      </c>
-      <c r="D3" t="s">
-        <v>369</v>
+        <v>420</v>
       </c>
       <c r="E3" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="B4" t="s">
-        <v>431</v>
-      </c>
-      <c r="C4" t="s">
-        <v>432</v>
-      </c>
-      <c r="D4" t="s">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="E4" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="B5" t="s">
-        <v>433</v>
-      </c>
-      <c r="C5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D5" t="s">
-        <v>369</v>
+        <v>424</v>
       </c>
       <c r="E5" t="s">
-        <v>396</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="B6" t="s">
-        <v>434</v>
-      </c>
-      <c r="C6" t="s">
-        <v>435</v>
-      </c>
-      <c r="D6" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="E6" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="B7" t="s">
-        <v>436</v>
-      </c>
-      <c r="C7" t="s">
-        <v>437</v>
-      </c>
-      <c r="D7" t="s">
-        <v>369</v>
+        <v>428</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="B8" t="s">
-        <v>438</v>
-      </c>
-      <c r="C8" t="s">
-        <v>439</v>
-      </c>
-      <c r="D8" t="s">
-        <v>369</v>
-      </c>
-      <c r="E8" t="s">
-        <v>392</v>
-      </c>
+      <c r="A8" s="9"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="9"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="9"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="9"/>
+      <c r="C11" s="8"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="9"/>
+      <c r="C12" s="8"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="9"/>
+      <c r="C13" s="8"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="9"/>
+      <c r="C14" s="8"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="9"/>
+      <c r="C15" s="8"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="9"/>
+      <c r="C16" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
